--- a/271025_Results_Med/output/input_famd_med_29102025.xlsx
+++ b/271025_Results_Med/output/input_famd_med_29102025.xlsx
@@ -862,7 +862,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q4">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q6">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q8">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q9">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q12">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q14">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q15">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q18">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="Q19">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q23">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q25">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q26">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q27">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="Q29">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q31">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q32">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q33">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q36">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Cuidado y familia (escuela, niñas/os)</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q37">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q38">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q40">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q42">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q48">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Cuidado y familia (recreación, niñas/os)</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q49">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q52">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q53">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="Q55">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q59">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="Q60">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q62">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q66">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q78">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q82">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q83">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q85">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q86">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q91">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="Q94">
@@ -12737,7 +12737,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Cuidado y familia (salud, niñas/os)</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q95">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q97">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q98">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q105">
@@ -14297,7 +14297,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q107">
@@ -14432,7 +14432,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q108">
@@ -14562,7 +14562,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q109">
@@ -14822,7 +14822,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q111">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q112">
@@ -15082,7 +15082,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q113">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q115">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q118">
@@ -15997,7 +15997,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Cuidado y familia (persona enferma)</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q120">
@@ -16127,7 +16127,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q121">
@@ -16522,7 +16522,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q124">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q126">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q127">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q129">
@@ -17437,7 +17437,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q131">
@@ -17567,7 +17567,7 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q132">
@@ -17697,7 +17697,7 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q133">
@@ -17962,7 +17962,7 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Cuidado y familia (escuela, niñas/os)</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q135">
@@ -18092,7 +18092,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q136">
@@ -18222,7 +18222,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="Q137">
@@ -18352,7 +18352,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q138">
@@ -18482,7 +18482,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q139">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q143">
@@ -19272,7 +19272,7 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q145">
@@ -19402,7 +19402,7 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q146">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="Q147">
@@ -19662,7 +19662,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q148">
@@ -19792,7 +19792,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q149">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="Q152">
@@ -20587,7 +20587,7 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q155">
@@ -20722,7 +20722,7 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q156">
@@ -20987,7 +20987,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q158">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q159">
@@ -21382,7 +21382,7 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q161">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q162">
@@ -21642,7 +21642,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="Q163">
@@ -21772,7 +21772,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="Q164">
@@ -22427,7 +22427,7 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q169">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q171">
@@ -22822,7 +22822,7 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q172">
@@ -23082,7 +23082,7 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q174">
@@ -23347,7 +23347,7 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q176">
@@ -23737,7 +23737,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q179">
@@ -24392,7 +24392,7 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q184">
@@ -24657,7 +24657,7 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q186">
@@ -25052,7 +25052,7 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q189">
@@ -25447,7 +25447,7 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q192">
@@ -25582,7 +25582,7 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q193">
@@ -25712,7 +25712,7 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q194">
@@ -25972,7 +25972,7 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q196">
@@ -26102,7 +26102,7 @@
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q197">
@@ -26362,7 +26362,7 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q199">
@@ -27142,7 +27142,7 @@
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q205">
@@ -27402,7 +27402,7 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q207">
@@ -27537,7 +27537,7 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q208">
@@ -27672,7 +27672,7 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="Q209">
@@ -28197,7 +28197,7 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q213">
@@ -28982,7 +28982,7 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q219">
@@ -29242,7 +29242,7 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q221">
@@ -29502,7 +29502,7 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q223">
@@ -29892,7 +29892,7 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q226">
@@ -30027,7 +30027,7 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q227">
@@ -30287,7 +30287,7 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q229">
@@ -30807,7 +30807,7 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q233">
@@ -30937,7 +30937,7 @@
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q234">
@@ -31457,7 +31457,7 @@
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q238">
@@ -31717,7 +31717,7 @@
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q240">
@@ -31847,7 +31847,7 @@
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q241">
@@ -31977,7 +31977,7 @@
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q242">
@@ -32107,7 +32107,7 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q243">
@@ -32237,7 +32237,7 @@
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q244">
@@ -32502,7 +32502,7 @@
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q246">
@@ -32762,7 +32762,7 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q248">
@@ -33677,7 +33677,7 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q255">
@@ -34202,7 +34202,7 @@
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q259">
@@ -34982,7 +34982,7 @@
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q265">
@@ -35372,7 +35372,7 @@
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q268">
@@ -35502,7 +35502,7 @@
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Cuidado y familia (escuela, niñas/os)</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q269">
@@ -35637,7 +35637,7 @@
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Cuidado y familia (persona con discapacidad)</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q270">
@@ -35767,7 +35767,7 @@
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q271">
@@ -35902,7 +35902,7 @@
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q272">
@@ -36032,7 +36032,7 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q273">
@@ -36292,7 +36292,7 @@
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q275">
@@ -36552,7 +36552,7 @@
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q277">
@@ -36682,7 +36682,7 @@
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q278">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="Q280">
@@ -37607,7 +37607,7 @@
       </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q285">
@@ -37737,7 +37737,7 @@
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q286">
@@ -38517,7 +38517,7 @@
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>Cuidado y familia (escuela, niñas/os)</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q292">
@@ -38782,7 +38782,7 @@
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q294">
@@ -38912,7 +38912,7 @@
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="Q295">
@@ -39177,7 +39177,7 @@
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q297">
@@ -39307,7 +39307,7 @@
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q298">
@@ -39572,7 +39572,7 @@
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q300">
@@ -39962,7 +39962,7 @@
       </c>
       <c r="P303" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q303">
@@ -40352,7 +40352,7 @@
       </c>
       <c r="P306" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q306">
@@ -41002,7 +41002,7 @@
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q311">
@@ -41537,7 +41537,7 @@
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>Cuidado y familia (escuela, niñas/os)</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q315">
@@ -42062,7 +42062,7 @@
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q319">
@@ -43367,7 +43367,7 @@
       </c>
       <c r="P329" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="Q329">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q330">
@@ -44022,7 +44022,7 @@
       </c>
       <c r="P334" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q334">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="P335" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q335">
@@ -44292,7 +44292,7 @@
       </c>
       <c r="P336" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="Q336">
@@ -44687,7 +44687,7 @@
       </c>
       <c r="P339" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q339">
@@ -44817,7 +44817,7 @@
       </c>
       <c r="P340" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q340">
@@ -48212,7 +48212,7 @@
       </c>
       <c r="P366" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q366">
@@ -48342,7 +48342,7 @@
       </c>
       <c r="P367" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q367">
@@ -48472,7 +48472,7 @@
       </c>
       <c r="P368" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q368">
@@ -48602,7 +48602,7 @@
       </c>
       <c r="P369" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q369">
@@ -48732,7 +48732,7 @@
       </c>
       <c r="P370" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q370">
@@ -49122,7 +49122,7 @@
       </c>
       <c r="P373" t="inlineStr">
         <is>
-          <t>Cuidado y familia (salud, niñas/os)</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q373">
@@ -49642,7 +49642,7 @@
       </c>
       <c r="P377" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q377">
@@ -49902,7 +49902,7 @@
       </c>
       <c r="P379" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q379">
@@ -50812,7 +50812,7 @@
       </c>
       <c r="P386" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q386">
@@ -51602,7 +51602,7 @@
       </c>
       <c r="P392" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q392">
@@ -52127,7 +52127,7 @@
       </c>
       <c r="P396" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="Q396">
@@ -53037,7 +53037,7 @@
       </c>
       <c r="P403" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="Q403">
@@ -53952,7 +53952,7 @@
       </c>
       <c r="P410" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q410">
@@ -54737,7 +54737,7 @@
       </c>
       <c r="P416" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="Q416">
